--- a/Affinity/Affinity_USG_All_Emails.xlsx
+++ b/Affinity/Affinity_USG_All_Emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://axpogrp-my.sharepoint.com/personal/thaddeaus_low_axpo_com/Documents/Desktop/SHIPPING BROKER REPORTS/Affinity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_23F921ED0CF3096DAF6540CCF1ECAE8B4F846538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23E5AEFD-682A-4E76-A918-A4E254F8EF0B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED0CF3096DAF6540CCF1ECAE8B4F846538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9634D36E-1C08-4B12-84C3-18E39959A1E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,6 +531,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -823,7 +827,18 @@
   <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="221.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Affinity/Affinity_USG_All_Emails.xlsx
+++ b/Affinity/Affinity_USG_All_Emails.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://axpogrp-my.sharepoint.com/personal/thaddeaus_low_axpo_com/Documents/Desktop/SHIPPING BROKER REPORTS/Affinity/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED0CF3096DAF6540CCF1ECAE8B4F846538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9634D36E-1C08-4B12-84C3-18E39959A1E9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -409,10 +403,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>2026-02-27 16:00:49</t>
-  </si>
-  <si>
-    <t>2026-02-27 16:01:04</t>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
   </si>
   <si>
     <t>C:\Users\THADLOW\OneDrive - Axpo Services AG\Desktop\SHIPPING BROKER REPORTS\Affinity\Emails\2026-02-27_160052__FW_ Affinity LPG - VLGC East Update - 27 Feb\2026-02-27_160052__FW_ Affinity LPG - VLGC East Update - 27 Feb.msg</t>
@@ -454,11 +448,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,25 +516,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -578,7 +560,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -612,7 +594,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -647,10 +628,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -823,26 +803,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="221.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -889,7 +854,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -936,7 +901,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -983,7 +948,7 @@
         <v>46098.5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +995,7 @@
         <v>46103.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1077,7 +1042,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1124,7 +1089,7 @@
         <v>46108.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1171,7 +1136,7 @@
         <v>46111.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1218,7 +1183,7 @@
         <v>46113.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1265,7 +1230,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1312,7 +1277,7 @@
         <v>46114.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1356,7 +1321,7 @@
         <v>46118.5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1403,7 +1368,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1450,7 +1415,7 @@
         <v>46117.5</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1497,7 +1462,7 @@
         <v>46118.5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1544,7 +1509,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1591,7 +1556,7 @@
         <v>46120.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1638,7 +1603,7 @@
         <v>46121.5</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1685,7 +1650,7 @@
         <v>46127.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1732,7 +1697,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1779,7 +1744,7 @@
         <v>46098.5</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1826,7 +1791,7 @@
         <v>46103.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1873,7 +1838,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1920,7 +1885,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -1967,7 +1932,7 @@
         <v>46108.5</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -2014,7 +1979,7 @@
         <v>46109.5</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -2061,7 +2026,7 @@
         <v>46111.5</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2108,7 +2073,7 @@
         <v>46113.5</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -2155,7 +2120,7 @@
         <v>46113.5</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -2202,7 +2167,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -2249,7 +2214,7 @@
         <v>46117.5</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2293,7 +2258,7 @@
         <v>46119.5</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2340,7 +2305,7 @@
         <v>46118.5</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2387,7 +2352,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -2434,7 +2399,7 @@
         <v>46121.5</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2484,10 +2449,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{008f8310-773b-421c-bb16-a09e7820894b}" enabled="1" method="Standard" siteId="{8619c67c-945a-48ae-8e77-35b1b71c9b98}" removed="0"/>
-</clbl:labelList>
 </file>